--- a/배포4/3_공통사용/인수인계함/1_결정대기_v10_261007.xlsx
+++ b/배포4/3_공통사용/인수인계함/1_결정대기_v10_261007.xlsx
@@ -2601,8 +2601,16 @@
           <t>28·37번</t>
         </is>
       </c>
-      <c r="I48" s="20" t="n"/>
-      <c r="J48" s="19" t="n"/>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-07 프로님 「이런 것도 못 하냐」 → 클로드가 복사함. 28·37번이 260922판을 집는 것 확인</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="96" customHeight="1">
       <c r="A49" s="19" t="inlineStr">

--- a/배포4/3_공통사용/인수인계함/1_결정대기_v10_261007.xlsx
+++ b/배포4/3_공통사용/인수인계함/1_결정대기_v10_261007.xlsx
@@ -2469,8 +2469,16 @@
           <t>28번 · /도면 · /견적</t>
         </is>
       </c>
-      <c r="I45" s="20" t="n"/>
-      <c r="J45" s="19" t="n"/>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-07 프로님 승인목록에 두 줄 적음 → 클로드가 t28_cost.precedent()·execsheet 고침 (커밋). 두 줄은 지우셔도 됩니다</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="96" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
@@ -2513,8 +2521,16 @@
           <t>28·37번 · 돈_게이트</t>
         </is>
       </c>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="19" t="n"/>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>답 없음 — 프로님 「이어서 작업해」 로 추천 ①(정답본대로 견적→실행)로 진행. 뒤집으시면 execsheet 열 순서만 되돌림</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>①로 진행</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="96" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
